--- a/data/Calf - Cow - Steer Sales - Stat Cards.xlsx
+++ b/data/Calf - Cow - Steer Sales - Stat Cards.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -472,30 +472,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cull Rate</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>% of cows</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Avg Cull Cow Price</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>per head</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Calf - Cow - Steer Sales - Stat Cards.xlsx
+++ b/data/Calf - Cow - Steer Sales - Stat Cards.xlsx
@@ -456,8 +456,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>calves, cull cows, steers</t>
-        </is>
+          <t>cows under 5 mos, over 2 yrs, 5-24 mos</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>880</v>
+      </c>
+      <c r="D2" t="n">
+        <v>754</v>
       </c>
     </row>
     <row r="3">
@@ -470,6 +476,12 @@
         <is>
           <t>all categories</t>
         </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1341581</v>
+      </c>
+      <c r="D3" t="n">
+        <v>845256.84</v>
       </c>
     </row>
   </sheetData>
